--- a/Unity/Assets/Config/Excel/UnitConfig.xlsx
+++ b/Unity/Assets/Config/Excel/UnitConfig.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\25046\Desktop\TOD\ET_HollowKnight\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E89D57E4-A79E-42BF-A0FA-FE67958365C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{662E9683-CED3-45B5-A307-37B65600CFCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2055" yWindow="2565" windowWidth="17115" windowHeight="12915" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
   <si>
     <t>#</t>
   </si>
@@ -108,13 +109,101 @@
   <si>
     <t>ragna</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能Id</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillName</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkilId</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>波动拳</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>升龙拳</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>升龙烈破</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>下中脚</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillType</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 -- 普通技能                        2 -- 特殊技能                3 -- 觉醒技能</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0 -- 上段                     1 -- 中段                    2 -- 下段</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能名</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能类型</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能层级</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫雷踵落(kk中段)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2Mk</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>26P</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>KKMK</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>623P</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2626P</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,6 +245,21 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -183,7 +287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -206,6 +310,22 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -695,4 +815,215 @@
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8372608B-98F9-436E-92BC-74A88BFAE995}">
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="4" max="4" width="15.25" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="22.875" customWidth="1"/>
+    <col min="7" max="7" width="11.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1">
+        <v>1001</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="13">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4">
+        <v>2</v>
+      </c>
+      <c r="H6" s="16"/>
+    </row>
+    <row r="7" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1">
+        <v>1002</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="4">
+        <v>2</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="16"/>
+    </row>
+    <row r="8" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1">
+        <v>1003</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="4">
+        <v>2</v>
+      </c>
+      <c r="G8" s="4">
+        <v>1</v>
+      </c>
+      <c r="H8" s="16"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9">
+        <v>1004</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="14">
+        <v>2</v>
+      </c>
+      <c r="G9" s="16">
+        <v>0</v>
+      </c>
+      <c r="H9" s="16"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9">
+        <v>1005</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="14">
+        <v>3</v>
+      </c>
+      <c r="G10" s="16">
+        <v>0</v>
+      </c>
+      <c r="H10" s="16"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/UnitConfig.xlsx
+++ b/Unity/Assets/Config/Excel/UnitConfig.xlsx
@@ -1,27 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\25046\Desktop\TOD\ET_HollowKnight\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{662E9683-CED3-45B5-A307-37B65600CFCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3EB8106-2E82-40C6-A265-78A7AAA70CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t>#</t>
   </si>
@@ -109,101 +108,13 @@
   <si>
     <t>ragna</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能Id</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillName</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkilId</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Id</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>波动拳</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>升龙拳</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>升龙烈破</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>下中脚</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillType</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1 -- 普通技能                        2 -- 特殊技能                3 -- 觉醒技能</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>0 -- 上段                     1 -- 中段                    2 -- 下段</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能名</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能类型</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能层级</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>紫雷踵落(kk中段)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>2Mk</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>26P</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>KKMK</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>623P</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>2626P</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,21 +156,6 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -287,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -310,22 +206,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -815,215 +695,4 @@
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8372608B-98F9-436E-92BC-74A88BFAE995}">
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="4" max="4" width="15.25" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="22.875" customWidth="1"/>
-    <col min="7" max="7" width="11.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1">
-        <v>1001</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="13">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4">
-        <v>2</v>
-      </c>
-      <c r="H6" s="16"/>
-    </row>
-    <row r="7" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1">
-        <v>1002</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="4">
-        <v>2</v>
-      </c>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" s="16"/>
-    </row>
-    <row r="8" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1">
-        <v>1003</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="4">
-        <v>2</v>
-      </c>
-      <c r="G8" s="4">
-        <v>1</v>
-      </c>
-      <c r="H8" s="16"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9">
-        <v>1004</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="14">
-        <v>2</v>
-      </c>
-      <c r="G9" s="16">
-        <v>0</v>
-      </c>
-      <c r="H9" s="16"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9">
-        <v>1005</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="14">
-        <v>3</v>
-      </c>
-      <c r="G10" s="16">
-        <v>0</v>
-      </c>
-      <c r="H10" s="16"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>